--- a/测试环境/小表2.xlsx
+++ b/测试环境/小表2.xlsx
@@ -5,49 +5,39 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c4e8455bcdffc71/Desktop/发送到服务器的文件/excel小表并大表/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9c4e8455bcdffc71/Desktop/excel小表并大表/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_AD4DA82427541F7ACA7EB8D5404B1EBE6AE8DE11" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{348F8928-2F28-41C2-B77A-AADD612E0F4A}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="11_AD4DA82427541F7ACA7EB8D5404B1EBE6AE8DE11" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F1EF344-06DB-429F-AC2E-4C5C15D7F24F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34290" yWindow="0" windowWidth="17415" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAME1" sheetId="1" r:id="rId1"/>
     <sheet name="NAME2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>1 1</t>
   </si>
@@ -65,6 +55,30 @@
   <si>
     <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>T T</t>
   </si>
 </sst>
 </file>
@@ -87,12 +101,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -107,8 +133,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -124,10 +155,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -397,29 +424,29 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>0</v>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -643,31 +670,31 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1">
+      <c r="A1" s="2">
         <v>1</v>
       </c>
-      <c r="B1">
+      <c r="B1" s="2">
         <v>11</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="2">
         <v>4</v>
       </c>
-      <c r="D1">
+      <c r="D1" s="3">
         <v>111</v>
       </c>
-      <c r="E1">
+      <c r="E1" s="2">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1">
+      <c r="F1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2">
         <v>3</v>
       </c>
-      <c r="I1">
+      <c r="I1" s="3">
         <v>3333</v>
       </c>
     </row>
@@ -682,7 +709,7 @@
         <v>51</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>77</v>
@@ -717,7 +744,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -858,7 +885,7 @@
         <v>12</v>
       </c>
       <c r="I9" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
